--- a/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N48_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N48_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>34.05165117831163</v>
+        <v>5.53339331647564</v>
       </c>
       <c r="D2" t="n">
-        <v>33.231339728359</v>
+        <v>5.400092705858338</v>
       </c>
       <c r="E2" t="n">
-        <v>9.338301065485945</v>
+        <v>1.517473923141466</v>
       </c>
       <c r="F2" t="n">
-        <v>9.604971304273525</v>
+        <v>1.560807836944448</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>32.33522497297212</v>
+        <v>5.25447405810797</v>
       </c>
       <c r="D3" t="n">
-        <v>32.39506956633929</v>
+        <v>5.264198804530135</v>
       </c>
       <c r="E3" t="n">
-        <v>9.338301065485945</v>
+        <v>1.517473923141466</v>
       </c>
       <c r="F3" t="n">
-        <v>9.604971304273525</v>
+        <v>1.560807836944448</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>30.27645356964526</v>
+        <v>4.919923705067355</v>
       </c>
       <c r="D4" t="n">
-        <v>30.68039640113513</v>
+        <v>4.985564415184458</v>
       </c>
       <c r="E4" t="n">
-        <v>9.338301065485945</v>
+        <v>1.517473923141466</v>
       </c>
       <c r="F4" t="n">
-        <v>9.604971304273525</v>
+        <v>1.560807836944448</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>47.46078206656377</v>
+        <v>7.712377085816613</v>
       </c>
       <c r="D5" t="n">
-        <v>46.34248783773388</v>
+        <v>7.530654273631757</v>
       </c>
       <c r="E5" t="n">
-        <v>9.338301065485945</v>
+        <v>1.517473923141466</v>
       </c>
       <c r="F5" t="n">
-        <v>9.604971304273525</v>
+        <v>1.560807836944448</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>28.05321643279747</v>
+        <v>4.558647670329589</v>
       </c>
       <c r="D6" t="n">
-        <v>26.94930314615814</v>
+        <v>4.379261761250698</v>
       </c>
       <c r="E6" t="n">
-        <v>9.338301065485945</v>
+        <v>1.517473923141466</v>
       </c>
       <c r="F6" t="n">
-        <v>9.604971304273525</v>
+        <v>1.560807836944448</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>35.56954760403631</v>
+        <v>5.780051485655901</v>
       </c>
       <c r="D7" t="n">
-        <v>36.5885554418413</v>
+        <v>5.945640259299211</v>
       </c>
       <c r="E7" t="n">
-        <v>9.338301065485945</v>
+        <v>1.517473923141466</v>
       </c>
       <c r="F7" t="n">
-        <v>9.604971304273525</v>
+        <v>1.560807836944448</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>19.56807442781995</v>
+        <v>3.179812094520742</v>
       </c>
       <c r="D8" t="n">
-        <v>18.70161482961799</v>
+        <v>3.039012409812924</v>
       </c>
       <c r="E8" t="n">
-        <v>9.338301065485945</v>
+        <v>1.517473923141466</v>
       </c>
       <c r="F8" t="n">
-        <v>9.604971304273525</v>
+        <v>1.560807836944448</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>41.15286810468359</v>
+        <v>6.687341067011084</v>
       </c>
       <c r="D9" t="n">
-        <v>42.27745439888337</v>
+        <v>6.870086339818548</v>
       </c>
       <c r="E9" t="n">
-        <v>9.338301065485945</v>
+        <v>1.517473923141466</v>
       </c>
       <c r="F9" t="n">
-        <v>9.604971304273525</v>
+        <v>1.560807836944448</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>34.1785887168223</v>
+        <v>5.554020666483624</v>
       </c>
       <c r="D10" t="n">
-        <v>33.38672235148011</v>
+        <v>5.425342382115518</v>
       </c>
       <c r="E10" t="n">
-        <v>9.338301065485945</v>
+        <v>1.517473923141466</v>
       </c>
       <c r="F10" t="n">
-        <v>9.604971304273525</v>
+        <v>1.560807836944448</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>19.80240816178788</v>
+        <v>3.217891326290531</v>
       </c>
       <c r="D11" t="n">
-        <v>19.73937478622785</v>
+        <v>3.207648402762026</v>
       </c>
       <c r="E11" t="n">
-        <v>9.338301065485945</v>
+        <v>1.517473923141466</v>
       </c>
       <c r="F11" t="n">
-        <v>9.604971304273525</v>
+        <v>1.560807836944448</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>25.6431089003795</v>
+        <v>4.167005196311669</v>
       </c>
       <c r="D12" t="n">
-        <v>26.56065129475465</v>
+        <v>4.31610583539763</v>
       </c>
       <c r="E12" t="n">
-        <v>9.338301065485945</v>
+        <v>1.517473923141466</v>
       </c>
       <c r="F12" t="n">
-        <v>9.604971304273525</v>
+        <v>1.560807836944448</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>49.71096592130881</v>
+        <v>8.07803196221268</v>
       </c>
       <c r="D13" t="n">
-        <v>50.77480935300309</v>
+        <v>8.250906519863003</v>
       </c>
       <c r="E13" t="n">
-        <v>9.338301065485945</v>
+        <v>1.517473923141466</v>
       </c>
       <c r="F13" t="n">
-        <v>9.604971304273525</v>
+        <v>1.560807836944448</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>44.96891953170043</v>
+        <v>7.30744942390132</v>
       </c>
       <c r="D14" t="n">
-        <v>45.55228982293213</v>
+        <v>7.402247096226471</v>
       </c>
       <c r="E14" t="n">
-        <v>9.338301065485945</v>
+        <v>1.517473923141466</v>
       </c>
       <c r="F14" t="n">
-        <v>9.604971304273525</v>
+        <v>1.560807836944448</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
